--- a/output/pdf_financials_xlsx/EFX.xlsx
+++ b/output/pdf_financials_xlsx/EFX.xlsx
@@ -5369,7 +5369,7 @@
         <v>142.492</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>142.492</v>
+        <v>224.271</v>
       </c>
       <c r="L91" s="1" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EFX.xlsx
+++ b/output/pdf_financials_xlsx/EFX.xlsx
@@ -4175,10 +4175,10 @@
         <v>2e-05</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>4e-05</v>
+        <v>708</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>0</v>
+        <v>582</v>
       </c>
     </row>
     <row r="70">
@@ -4283,10 +4283,10 @@
         <v>0.020145</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>4e-05</v>
+        <v>708</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>582</v>
       </c>
     </row>
     <row r="72">
@@ -4502,7 +4502,7 @@
         <v>6e-06</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4609,10 +4609,10 @@
         <v>0.001007</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>2832</v>
+        <v>2124</v>
       </c>
       <c r="P77" s="3" t="n">
-        <v>2328</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="78">
@@ -4717,10 +4717,10 @@
         <v>0.001007</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>2832</v>
+        <v>2124</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>2328</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="80">
@@ -4777,7 +4777,7 @@
         <v>18.55438596491228</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>2.699714051477598</v>
+        <v>2.699714013346044</v>
       </c>
       <c r="P80" s="3" t="n">
         <v>2.129917657822507</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">

--- a/output/pdf_financials_xlsx/EFX.xlsx
+++ b/output/pdf_financials_xlsx/EFX.xlsx
@@ -1048,37 +1048,37 @@
         <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.005518</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.009787000000000001</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.01531</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.014056</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-31.872</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-37.723</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-21.164</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.016995</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.038923</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>-9.399999999999999e-05</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>-9.8e-05</v>
       </c>
       <c r="P13" s="1" t="inlineStr">
         <is>
@@ -1886,37 +1886,37 @@
         <v>0.11278</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.082381</v>
+        <v>0.087899</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.129135</v>
+        <v>0.138922</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.079567</v>
+        <v>0.094877</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.095528</v>
+        <v>-0.081472</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>133.068</v>
+        <v>164.94</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>132.534</v>
+        <v>170.257</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>215.324</v>
+        <v>236.488</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.038102</v>
+        <v>0.055097</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.079733</v>
+        <v>-0.04081</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.06852800000000001</v>
+        <v>-0.06843399999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>32.000049</v>
+        <v>32.000147</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
@@ -1994,37 +1994,37 @@
         <v>0.152267</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.121976</v>
+        <v>0.127494</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.185934</v>
+        <v>0.195721</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.162338</v>
+        <v>0.177648</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.002429</v>
+        <v>0.011627</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>213.646</v>
+        <v>245.518</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>222.308</v>
+        <v>260.031</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>301.883</v>
+        <v>323.047</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.125724</v>
+        <v>0.142719</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.048554</v>
+        <v>0.087477</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.06833</v>
+        <v>-0.068236</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>79.000049</v>
+        <v>79.000147</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2048,37 +2048,37 @@
         <v>10.13974977425344</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>8.681429899318301</v>
+        <v>9.074163963268903</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>10.96179695790591</v>
+        <v>11.53879259521283</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>9.965304548959136</v>
+        <v>10.90512648002004</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-0.2148409168904409</v>
+        <v>1.028388365864618</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>13.7538424893215</v>
+        <v>15.80565936312047</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>13.05181259845016</v>
+        <v>15.26654858029218</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>14.75895927588537</v>
+        <v>15.79366018357092</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>13.09412220514166</v>
+        <v>14.86414707610014</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>2.731131433379945</v>
+        <v>4.920525279024951</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-2916.346564233888</v>
+        <v>-2912.334613743064</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>3272578.666114333</v>
+        <v>3272582.725766363</v>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
@@ -77559,7 +77559,11 @@
           <t>Earnings before finance costs and income taxes (“EBIT”)</t>
         </is>
       </c>
-      <c r="D776" t="inlineStr"/>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E776" t="inlineStr">
         <is>
           <t>-</t>
@@ -77644,7 +77648,11 @@
           <t>Net finance costs (Note 25)</t>
         </is>
       </c>
-      <c r="D777" t="inlineStr"/>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E777" t="inlineStr">
         <is>
           <t>-</t>
@@ -79627,7 +79635,11 @@
           <t>Net finance costs (Note 28)</t>
         </is>
       </c>
-      <c r="D800" t="inlineStr"/>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E800" t="inlineStr">
         <is>
           <t>-</t>
@@ -80586,7 +80598,11 @@
           <t>Net finance costs (Note 27)</t>
         </is>
       </c>
-      <c r="D811" t="inlineStr"/>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E811" t="inlineStr">
         <is>
           <t>-</t>
@@ -81258,7 +81274,7 @@
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E819" s="5" t="n">
@@ -82838,7 +82854,7 @@
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
@@ -82929,7 +82945,11 @@
           <t>Net finance costs i 15,992</t>
         </is>
       </c>
-      <c r="D838" t="inlineStr"/>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E838" t="inlineStr">
         <is>
           <t>-</t>
@@ -85200,7 +85220,7 @@
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
@@ -85291,7 +85311,11 @@
           <t>Net finance costs 19,145</t>
         </is>
       </c>
-      <c r="D864" t="inlineStr"/>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E864" t="inlineStr">
         <is>
           <t>-</t>
